--- a/UI_Enterprise_Transformation/LO1.xlsx
+++ b/UI_Enterprise_Transformation/LO1.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t xml:space="preserve">Risk Tracking Template MAUIS</t>
   </si>
@@ -254,6 +254,67 @@
   </si>
   <si>
     <t xml:space="preserve">Scrum Master, ProductOwner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication breakdown with
+Forestry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordination for the conservation event suffers,
+brand confidence suffers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Written contractual agreements with dates, fallback dates, organisational points of contact and fallback contacts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management
+Legal Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Users spoof screen time reduction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unusable data, unachievable costs of conservation
+to meet spoofed user achievements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feasible caps for trees planted in an event, logistics for maximum considered and agreed upon in signed documentation. 
+Good faith expectation based on no cash prizes. Daily cap of reduction in-app.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management
+Legal &amp; Dev Teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss of data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forestry team has no data to action 
+conservation event around.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data is always held on the user device so individual reporting can always be collated
+ into a document and delivered to the Forestry team manually.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forestry suffers logistics breakdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unable to plant trees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event can be rearranged or replacement materials and equipment used from throughout
+the organisation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forestry/ Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adverse weather prevents Forestry 
+event.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Events can be rearranged with little issue. Specific dates are not promised but rather are approximate. Users are update with the latest information.</t>
   </si>
   <si>
     <t>Introduction</t>
@@ -493,14 +554,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="12.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.000000"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -621,7 +682,7 @@
     <xf fontId="4" fillId="4" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
     <xf fontId="5" fillId="5" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="6" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -683,26 +744,48 @@
     <xf fontId="11" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="11" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="4" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="4" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf fontId="11" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="5" fillId="5" borderId="4" numFmtId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="4" numFmtId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="5" fillId="5" borderId="4" numFmtId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="4" numFmtId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="11" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="11" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf fontId="12" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="13" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="13" fillId="6" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf fontId="13" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="12" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1949,14 +2032,28 @@
       <c r="A24" s="21">
         <v>19</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="22"/>
+      <c r="B24" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" s="25"/>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
@@ -1964,117 +2061,185 @@
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
     </row>
-    <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" ht="16.5">
-      <c r="A29" s="26"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
+    <row r="25" ht="33" customHeight="1">
+      <c r="A25" s="21">
+        <v>20</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+    </row>
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="21">
+        <v>21</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I26" s="25"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+    </row>
+    <row r="27" ht="32.25" customHeight="1">
+      <c r="A27" s="21">
+        <v>22</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="25"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+    </row>
+    <row r="28" ht="33">
+      <c r="A28" s="21">
+        <v>23</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+    </row>
+    <row r="29" ht="33" customHeight="1">
+      <c r="A29" s="21">
+        <v>24</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+    </row>
+    <row r="30" ht="31.5" customHeight="1">
+      <c r="A30" s="30">
+        <v>25</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
     </row>
     <row r="31">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
-      <c r="C31" s="23"/>
+      <c r="C31" s="32"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="25"/>
+      <c r="H31" s="33"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -2086,12 +2251,12 @@
     <row r="32">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
-      <c r="C32" s="23"/>
+      <c r="C32" s="32"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="25"/>
+      <c r="H32" s="33"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -2103,29 +2268,29 @@
     <row r="33" ht="16.5">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="23"/>
+      <c r="C33" s="32"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="25"/>
+      <c r="H33" s="33"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
     </row>
     <row r="34">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
-      <c r="C34" s="23"/>
+      <c r="C34" s="32"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="25"/>
+      <c r="H34" s="33"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -2137,12 +2302,12 @@
     <row r="35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
-      <c r="C35" s="23"/>
+      <c r="C35" s="32"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="25"/>
+      <c r="H35" s="33"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -2170,53 +2335,53 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="s">
-        <v>79</v>
+      <c r="A1" s="35" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" ht="57.600000000000001">
-      <c r="A3" s="30" t="s">
-        <v>80</v>
+      <c r="A3" s="36" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="s">
-        <v>81</v>
+      <c r="A5" s="37" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/UI_Enterprise_Transformation/LO1.xlsx
+++ b/UI_Enterprise_Transformation/LO1.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t xml:space="preserve">Risk Tracking Template MAUIS</t>
   </si>
@@ -315,6 +315,18 @@
   </si>
   <si>
     <t xml:space="preserve">Events can be rearranged with little issue. Specific dates are not promised but rather are approximate. Users are update with the latest information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security vulnerability in the Software Supply Chain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security vulnerability affects the app, possible malicious code injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrate Software Bill of Materials (SBOM) software into the CI/CD pipeline like dependency trackers to keep aware of any flagged vulnerabilities in the software supply chain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev and DevOps Team</t>
   </si>
   <si>
     <t>Introduction</t>
@@ -2197,13 +2209,27 @@
       <c r="A29" s="21">
         <v>24</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="22"/>
+      <c r="B29" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>99</v>
+      </c>
       <c r="I29" s="25"/>
       <c r="J29" s="18"/>
       <c r="K29" s="18"/>
@@ -2336,52 +2362,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="35" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" ht="57.600000000000001">
       <c r="A3" s="36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="37" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
